--- a/artfynd/A 20418-2023 artfynd.xlsx
+++ b/artfynd/A 20418-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20418-2023 artfynd.xlsx
+++ b/artfynd/A 20418-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109972599</v>
+        <v>109972597</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>540036.2769878758</v>
+        <v>540246</v>
       </c>
       <c r="R2" t="n">
-        <v>7194406.382128693</v>
+        <v>7194405</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109972596</v>
+        <v>109972614</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>540246.9754416416</v>
+        <v>540118</v>
       </c>
       <c r="R3" t="n">
-        <v>7194407.927399682</v>
+        <v>7194620</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109972597</v>
+        <v>109972594</v>
       </c>
       <c r="B4" t="n">
-        <v>76504</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>314</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>540246.1641461449</v>
+        <v>540243</v>
       </c>
       <c r="R4" t="n">
-        <v>7194404.940256377</v>
+        <v>7194435</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109972590</v>
+        <v>109972592</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>540249.5253370604</v>
+        <v>540273</v>
       </c>
       <c r="R5" t="n">
-        <v>7194535.087417194</v>
+        <v>7194508</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109972604</v>
+        <v>109972593</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>540059.4073783029</v>
+        <v>540275</v>
       </c>
       <c r="R6" t="n">
-        <v>7194459.412710484</v>
+        <v>7194474</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109972609</v>
+        <v>109972585</v>
       </c>
       <c r="B7" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>540095.447920289</v>
+        <v>540241</v>
       </c>
       <c r="R7" t="n">
-        <v>7194470.098539025</v>
+        <v>7194595</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,15 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109972586</v>
+        <v>109972589</v>
       </c>
       <c r="B8" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>540254.6561797312</v>
+        <v>540225</v>
       </c>
       <c r="R8" t="n">
-        <v>7194596.803997629</v>
+        <v>7194563</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109972580</v>
+        <v>109972595</v>
       </c>
       <c r="B9" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>540190.5210518551</v>
+        <v>540242</v>
       </c>
       <c r="R9" t="n">
-        <v>7194618.051389792</v>
+        <v>7194436</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,37 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109972577</v>
+        <v>109972581</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>540051.4840104239</v>
+        <v>540191</v>
       </c>
       <c r="R10" t="n">
-        <v>7194606.412342211</v>
+        <v>7194622</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,37 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109972610</v>
+        <v>109972603</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>540087.7067057617</v>
+        <v>540059</v>
       </c>
       <c r="R11" t="n">
-        <v>7194507.83486542</v>
+        <v>7194458</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,15 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109972603</v>
+        <v>109972605</v>
       </c>
       <c r="B12" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,21 +1756,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>540058.5675142389</v>
+        <v>540083</v>
       </c>
       <c r="R12" t="n">
-        <v>7194458.551147723</v>
+        <v>7194437</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,15 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109972615</v>
+        <v>109972607</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>540116.4287364801</v>
+        <v>540088</v>
       </c>
       <c r="R13" t="n">
-        <v>7194620.03511229</v>
+        <v>7194447</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,15 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109972588</v>
+        <v>109972616</v>
       </c>
       <c r="B14" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>540229.1342445153</v>
+        <v>540111</v>
       </c>
       <c r="R14" t="n">
-        <v>7194563.724542256</v>
+        <v>7194625</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,15 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109972581</v>
+        <v>109972578</v>
       </c>
       <c r="B15" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>540190.4640694644</v>
+        <v>540052</v>
       </c>
       <c r="R15" t="n">
-        <v>7194622.302111876</v>
+        <v>7194609</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2206,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,15 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109972589</v>
+        <v>109972582</v>
       </c>
       <c r="B16" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2259,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>540225.3152799477</v>
+        <v>540290</v>
       </c>
       <c r="R16" t="n">
-        <v>7194562.822988532</v>
+        <v>7194603</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2318,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,15 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>109972600</v>
+        <v>109972583</v>
       </c>
       <c r="B17" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>540031.0617241267</v>
+        <v>540276</v>
       </c>
       <c r="R17" t="n">
-        <v>7194414.390869419</v>
+        <v>7194601</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2430,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,15 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109972578</v>
+        <v>109972586</v>
       </c>
       <c r="B18" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2507,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>540051.4442607693</v>
+        <v>540255</v>
       </c>
       <c r="R18" t="n">
-        <v>7194609.387859418</v>
+        <v>7194597</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2542,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,15 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>109972582</v>
+        <v>109972591</v>
       </c>
       <c r="B19" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2619,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>540289.4861805423</v>
+        <v>540249</v>
       </c>
       <c r="R19" t="n">
-        <v>7194602.37367175</v>
+        <v>7194538</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2654,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,37 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>109972584</v>
+        <v>109972599</v>
       </c>
       <c r="B20" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2809</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>540252.5909966561</v>
+        <v>540036</v>
       </c>
       <c r="R20" t="n">
-        <v>7194592.099592458</v>
+        <v>7194406</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2766,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,15 +2708,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>109972592</v>
+        <v>109972600</v>
       </c>
       <c r="B21" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,21 +2719,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>540272.8732116893</v>
+        <v>540031</v>
       </c>
       <c r="R21" t="n">
-        <v>7194508.190520632</v>
+        <v>7194414</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2878,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,15 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>109972611</v>
+        <v>109972604</v>
       </c>
       <c r="B22" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2955,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>540091.8661204004</v>
+        <v>540060</v>
       </c>
       <c r="R22" t="n">
-        <v>7194515.118261834</v>
+        <v>7194460</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2990,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,15 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>109972591</v>
+        <v>109972609</v>
       </c>
       <c r="B23" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3067,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>540249.4853910661</v>
+        <v>540096</v>
       </c>
       <c r="R23" t="n">
-        <v>7194538.06300559</v>
+        <v>7194470</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3102,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,15 +3029,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>109972587</v>
+        <v>109972611</v>
       </c>
       <c r="B24" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3155,21 +3040,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>540229.1228371289</v>
+        <v>540092</v>
       </c>
       <c r="R24" t="n">
-        <v>7194564.574702553</v>
+        <v>7194515</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3214,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,15 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>109972594</v>
+        <v>109972612</v>
       </c>
       <c r="B25" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3267,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>540242.7797136331</v>
+        <v>540126</v>
       </c>
       <c r="R25" t="n">
-        <v>7194435.082405607</v>
+        <v>7194545</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3326,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,15 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>109972576</v>
+        <v>109972613</v>
       </c>
       <c r="B26" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,39 +3254,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gottnatjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>540041.4399553459</v>
+        <v>540101</v>
       </c>
       <c r="R26" t="n">
-        <v>7194625.409867583</v>
+        <v>7194546</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3443,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3453,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3480,37 +3350,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>109972605</v>
+        <v>109972584</v>
       </c>
       <c r="B27" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>2809</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3520,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>540082.697272729</v>
+        <v>540253</v>
       </c>
       <c r="R27" t="n">
-        <v>7194436.764658934</v>
+        <v>7194592</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3555,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3565,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3592,37 +3457,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>109972595</v>
+        <v>109972580</v>
       </c>
       <c r="B28" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3632,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>540241.9170726715</v>
+        <v>540191</v>
       </c>
       <c r="R28" t="n">
-        <v>7194435.921177411</v>
+        <v>7194618</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3667,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3677,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3704,37 +3564,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>109972616</v>
+        <v>109972577</v>
       </c>
       <c r="B29" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3744,10 +3599,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>540110.4022516678</v>
+        <v>540052</v>
       </c>
       <c r="R29" t="n">
-        <v>7194625.056255264</v>
+        <v>7194607</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3779,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3789,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3816,37 +3671,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>109972602</v>
+        <v>109972587</v>
       </c>
       <c r="B30" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3856,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>540022.1010514726</v>
+        <v>540229</v>
       </c>
       <c r="R30" t="n">
-        <v>7194415.971955951</v>
+        <v>7194565</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3891,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3901,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3928,15 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>109972614</v>
+        <v>109972596</v>
       </c>
       <c r="B31" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3944,21 +3789,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3968,10 +3813,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>540118.5566800712</v>
+        <v>540247</v>
       </c>
       <c r="R31" t="n">
-        <v>7194620.06358629</v>
+        <v>7194408</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4003,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4013,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4040,37 +3885,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>109972607</v>
+        <v>109972606</v>
       </c>
       <c r="B32" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4080,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>540087.6682430682</v>
+        <v>540089</v>
       </c>
       <c r="R32" t="n">
-        <v>7194447.035277712</v>
+        <v>7194444</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4115,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4125,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4152,37 +3992,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>109972583</v>
+        <v>109972610</v>
       </c>
       <c r="B33" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4192,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>540275.4530878684</v>
+        <v>540088</v>
       </c>
       <c r="R33" t="n">
-        <v>7194601.334821075</v>
+        <v>7194508</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4227,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4237,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4264,37 +4099,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>109972613</v>
+        <v>109972615</v>
       </c>
       <c r="B34" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4304,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>540100.3944430985</v>
+        <v>540117</v>
       </c>
       <c r="R34" t="n">
-        <v>7194545.843897758</v>
+        <v>7194620</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4339,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4349,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4376,15 +4206,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>109972585</v>
+        <v>109972602</v>
       </c>
       <c r="B35" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4392,21 +4217,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4416,10 +4241,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>540240.6344622419</v>
+        <v>540022</v>
       </c>
       <c r="R35" t="n">
-        <v>7194594.915157161</v>
+        <v>7194416</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4451,7 +4276,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4461,7 +4286,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4488,15 +4313,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>109972593</v>
+        <v>109972590</v>
       </c>
       <c r="B36" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4504,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4528,10 +4348,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>540275.4580508819</v>
+        <v>540250</v>
       </c>
       <c r="R36" t="n">
-        <v>7194474.211866794</v>
+        <v>7194535</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4563,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4573,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4600,37 +4420,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>109972612</v>
+        <v>109972608</v>
       </c>
       <c r="B37" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4640,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>540126.3673740926</v>
+        <v>540100</v>
       </c>
       <c r="R37" t="n">
-        <v>7194545.341077633</v>
+        <v>7194470</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4675,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4685,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4712,15 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>109972606</v>
+        <v>109972576</v>
       </c>
       <c r="B38" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4728,34 +4538,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gottnatjärnarna, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>540088.5592555696</v>
+        <v>540042</v>
       </c>
       <c r="R38" t="n">
-        <v>7194444.07098078</v>
+        <v>7194625</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4787,7 +4602,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4797,7 +4612,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4821,230 +4636,6 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>109972598</v>
-      </c>
-      <c r="B39" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Gottnatjärnarna, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>540087.3910498567</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7194404.088827975</v>
-      </c>
-      <c r="S39" t="n">
-        <v>25</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2023-06-10</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2023-06-10</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Isak Vahlström, Tove Lönneborg</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>109972608</v>
-      </c>
-      <c r="B40" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>6463</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Bårdlav</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Gottnatjärnarna, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>540100.5552401853</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7194470.166842675</v>
-      </c>
-      <c r="S40" t="n">
-        <v>25</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2023-06-10</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2023-06-10</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Isak Vahlström, Tove Lönneborg</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
